--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-27.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_2B59D187542ABD42A3B93A1159BCE0F26C35D2BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{944682EA-565C-4DC1-A4A8-BC6962E7332F}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_2B59D187542ABD42A3B93A1159BCE0F26C35D2BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEA42CC9-B2E5-465D-86E2-AC6BDC8204A1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,9 +103,6 @@
     <t>LAY</t>
   </si>
   <si>
-    <t>vs</t>
-  </si>
-  <si>
     <t>PENDENTE</t>
   </si>
   <si>
@@ -257,6 +254,9 @@
   </si>
   <si>
     <t>1x1</t>
+  </si>
+  <si>
+    <t>2x0</t>
   </si>
 </sst>
 </file>
@@ -332,6 +332,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -719,13 +723,13 @@
         <v>200</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" t="s">
         <v>28</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -733,25 +737,25 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>33</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
@@ -769,13 +773,13 @@
         <v>200</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" t="s">
         <v>28</v>
-      </c>
-      <c r="R3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -783,19 +787,19 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>39</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
       </c>
       <c r="G4" t="s">
         <v>24</v>
@@ -819,13 +823,13 @@
         <v>200</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" t="s">
         <v>28</v>
-      </c>
-      <c r="R4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -833,25 +837,25 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>42</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>43</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>44</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>45</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>46</v>
-      </c>
-      <c r="H5" t="s">
-        <v>47</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -869,13 +873,13 @@
         <v>200</v>
       </c>
       <c r="N5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" t="s">
         <v>28</v>
-      </c>
-      <c r="R5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -883,25 +887,25 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>50</v>
       </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
       <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
         <v>46</v>
-      </c>
-      <c r="H6" t="s">
-        <v>47</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
@@ -919,13 +923,13 @@
         <v>200</v>
       </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O6" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" t="s">
         <v>28</v>
-      </c>
-      <c r="R6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -933,25 +937,25 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
         <v>52</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>53</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>54</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>55</v>
       </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
       <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
         <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -969,13 +973,13 @@
         <v>200</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O7" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" t="s">
         <v>28</v>
-      </c>
-      <c r="R7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -983,25 +987,25 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
         <v>57</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>58</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>59</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>60</v>
-      </c>
-      <c r="H8" t="s">
-        <v>61</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1019,13 +1023,13 @@
         <v>300</v>
       </c>
       <c r="N8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O8" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" t="s">
         <v>28</v>
-      </c>
-      <c r="R8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -1033,19 +1037,19 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>63</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>64</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -1069,13 +1073,13 @@
         <v>200</v>
       </c>
       <c r="N9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" t="s">
         <v>28</v>
-      </c>
-      <c r="R9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -1083,25 +1087,25 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
         <v>67</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>68</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>69</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>70</v>
       </c>
-      <c r="F10" t="s">
-        <v>71</v>
-      </c>
       <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" t="s">
         <v>46</v>
-      </c>
-      <c r="H10" t="s">
-        <v>47</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1119,13 +1123,13 @@
         <v>200</v>
       </c>
       <c r="N10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O10" t="s">
         <v>27</v>
       </c>
-      <c r="O10" t="s">
+      <c r="R10" t="s">
         <v>28</v>
-      </c>
-      <c r="R10" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
